--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_309_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_309_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.946</v>
+        <v>5.1545</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1421</v>
+        <v>3.9809</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8038999999999999</v>
+        <v>1.1736</v>
       </c>
       <c r="G2" t="n">
         <v>1.5239</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7402</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5272</v>
+        <v>0.3659</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.2674</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>2.5387</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8651</v>
+        <v>4.6571</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8414</v>
+        <v>3.6671</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0237</v>
+        <v>0.9901</v>
       </c>
       <c r="G3" t="n">
         <v>2.9424</v>
@@ -688,13 +688,13 @@
         <v>2.0876</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6856</v>
+        <v>-0.8935</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6721</v>
+        <v>0.1535</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0135</v>
+        <v>-1.0471</v>
       </c>
       <c r="V3" t="n">
         <v>2.1444</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7579</v>
+        <v>2.646</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7031</v>
+        <v>2.9098</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9451</v>
+        <v>-0.2638</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3172</v>
+        <v>1.6967</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4547</v>
+        <v>1.5594</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1376</v>
+        <v>0.1373</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1464</v>
+        <v>2.1579</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1231</v>
+        <v>1.385</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0234</v>
+        <v>0.7729</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8293</v>
+        <v>-0.4612</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3317</v>
+        <v>0.1744</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1609</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1366</v>
+        <v>-0.4296</v>
       </c>
       <c r="T4" t="n">
-        <v>3.8219</v>
+        <v>-0.1452</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6853</v>
+        <v>-0.2844</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.5387</v>
       </c>
       <c r="W4" t="n">
-        <v>2.2862</v>
+        <v>3.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2862</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9137</v>
+        <v>0.5462</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0094</v>
+        <v>0.348</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0958</v>
+        <v>0.1982</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6967</v>
+        <v>0.6519</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5594</v>
+        <v>-0.2616</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1373</v>
+        <v>0.9135</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1579</v>
+        <v>0.509</v>
       </c>
       <c r="K5" t="n">
-        <v>1.385</v>
+        <v>0.1176</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7729</v>
+        <v>0.3914</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4612</v>
+        <v>0.1428</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1744</v>
+        <v>-0.3792</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.5221</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1619</v>
+        <v>-0.5179</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0455</v>
+        <v>0.0709</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1164</v>
+        <v>-0.5889</v>
       </c>
       <c r="V5" t="n">
-        <v>2.5387</v>
+        <v>-0.2836</v>
       </c>
       <c r="W5" t="n">
-        <v>3.2166</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.588</v>
+        <v>0.4028</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3722</v>
+        <v>0.2543</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2158</v>
+        <v>0.1485</v>
       </c>
       <c r="G6" t="n">
         <v>0.0195</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1274</v>
+        <v>-0.3126</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4129</v>
+        <v>0.295</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5403</v>
+        <v>-0.6075</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4961</v>
+        <v>0.3955</v>
       </c>
       <c r="E7" t="n">
-        <v>0.466</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0302</v>
+        <v>0.3871</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6519</v>
+        <v>2.0616</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2616</v>
+        <v>0.0374</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9135</v>
+        <v>2.0241</v>
       </c>
       <c r="J7" t="n">
-        <v>0.509</v>
+        <v>2.5871</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1176</v>
+        <v>-0.598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3914</v>
+        <v>3.1851</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1428</v>
+        <v>-0.5255</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3792</v>
+        <v>0.6354</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5221</v>
+        <v>-1.1609</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.9702</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1889</v>
+        <v>-0.0272</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7569</v>
+        <v>-0.9429</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3717</v>
+        <v>0.3899</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5488</v>
+        <v>2.5367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9205</v>
+        <v>-2.1468</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1876</v>
+        <v>0.3172</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5355</v>
+        <v>1.4547</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.348</v>
+        <v>-1.1376</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.091</v>
+        <v>1.1464</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6218</v>
+        <v>1.1231</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7127</v>
+        <v>0.0234</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2785</v>
+        <v>-0.8293</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0862</v>
+        <v>0.3317</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3648</v>
+        <v>-1.1609</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2618</v>
+        <v>0.7685999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1142</v>
+        <v>1.6555</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.376</v>
+        <v>-0.8869</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8197</v>
+        <v>2.2862</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0612</v>
+        <v>0.2203</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2658</v>
+        <v>-0.0732</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3271</v>
+        <v>0.2935</v>
       </c>
       <c r="G9" t="n">
         <v>-0.1168</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5926</v>
+        <v>-0.4336</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0351</v>
+        <v>0.1575</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5575</v>
+        <v>-0.5911</v>
       </c>
       <c r="V9" t="n">
         <v>1.4665</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.0329</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.0099</v>
+        <v>-1.0206</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2191</v>
+        <v>0.9877</v>
       </c>
       <c r="G10" t="n">
-        <v>2.0616</v>
+        <v>0.1876</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0374</v>
+        <v>0.5355</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0241</v>
+        <v>-0.348</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5871</v>
+        <v>-0.091</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.598</v>
+        <v>0.6218</v>
       </c>
       <c r="L10" t="n">
-        <v>3.1851</v>
+        <v>-0.7127</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5255</v>
+        <v>0.2785</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6354</v>
+        <v>-0.0862</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1609</v>
+        <v>0.3648</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1565</v>
+        <v>-0.6664</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0455</v>
+        <v>-0.3576</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.111</v>
+        <v>-0.3088</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6474</v>
+        <v>-3.4444</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4823</v>
+        <v>-3.0105</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1651</v>
+        <v>-0.4339</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9931</v>
@@ -1312,13 +1312,13 @@
         <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6001</v>
+        <v>-0.3971</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6721</v>
+        <v>-0.2003</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0721</v>
+        <v>-0.1968</v>
       </c>
       <c r="V11" t="n">
         <v>-1.214</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.5615</v>
+        <v>10.935</v>
       </c>
       <c r="E12" t="n">
-        <v>9.227400000000001</v>
+        <v>9.600899999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3343</v>
+        <v>1.3342</v>
       </c>
       <c r="G12" t="n">
         <v>6.290900000000001</v>
@@ -1366,7 +1366,7 @@
         <v>8.257999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>2.704600000000001</v>
+        <v>2.7046</v>
       </c>
       <c r="L12" t="n">
         <v>5.5535</v>
@@ -1390,13 +1390,13 @@
         <v>15.0769</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.757499999999999</v>
+        <v>-4.3841</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5948</v>
+        <v>1.968</v>
       </c>
       <c r="U12" t="n">
-        <v>-6.3522</v>
+        <v>-6.352099999999999</v>
       </c>
       <c r="V12" t="n">
         <v>7.868599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9704</v>
+        <v>2.8969</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3343</v>
+        <v>4.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3639</v>
+        <v>-1.2631</v>
       </c>
       <c r="G13" t="n">
         <v>4.0501</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9353</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5895</v>
+        <v>0.2361</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3457</v>
+        <v>-0.2449</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. DIBARTOLOMEO</t>
+          <t>W. RAYMAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6775</v>
+        <v>0.4863</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7924</v>
+        <v>1.6612</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1149</v>
+        <v>-1.175</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3545</v>
+        <v>-0.3493</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.2676</v>
+        <v>1.0961</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-1.4454</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5105</v>
+        <v>0.2547</v>
       </c>
       <c r="K14" t="n">
-        <v>0.4369</v>
+        <v>0.8571</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0736</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.8651</v>
+        <v>-0.604</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7045</v>
+        <v>0.2391</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1605</v>
+        <v>-0.8431</v>
       </c>
       <c r="P14" t="n">
         <v>0.9278</v>
@@ -1546,28 +1546,28 @@
         <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1764</v>
+        <v>-0.4865</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2819</v>
+        <v>0.3343</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1054</v>
+        <v>-0.8208</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>W. RAYMAN</t>
+          <t>J. DIBARTOLOMEO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5541</v>
+        <v>0.4073</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8971</v>
+        <v>1.3206</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.343</v>
+        <v>-0.9133</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3493</v>
+        <v>-0.3545</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0961</v>
+        <v>-0.2676</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4454</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2547</v>
+        <v>0.5105</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8571</v>
+        <v>0.4369</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.0736</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.604</v>
+        <v>-0.8651</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2391</v>
+        <v>-0.7045</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8431</v>
+        <v>-0.1605</v>
       </c>
       <c r="P15" t="n">
         <v>0.9278</v>
@@ -1624,28 +1624,28 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4187</v>
+        <v>0.9063</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5702</v>
+        <v>0.8101</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9889</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. BRISSETT</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0331</v>
+        <v>-0.0133</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0728</v>
+        <v>2.324</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0397</v>
+        <v>-2.3373</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.0567</v>
+        <v>1.0186</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.1333</v>
+        <v>1.0888</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9234</v>
+        <v>-0.0702</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.2702</v>
+        <v>1.1795</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.6679</v>
+        <v>1.1427</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7865</v>
+        <v>-0.1609</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4655</v>
+        <v>-0.0539</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3211</v>
+        <v>-0.107</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>4.0719</v>
+        <v>1.0429</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7526</v>
+        <v>1.0027</v>
       </c>
       <c r="U16" t="n">
-        <v>1.3192</v>
+        <v>0.0402</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-2.5387</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.428</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2961</v>
+        <v>-0.1445</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8885</v>
+        <v>1.0065</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1847</v>
+        <v>-1.151</v>
       </c>
       <c r="G17" t="n">
         <v>2.9156</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1937</v>
+        <v>-0.0422</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0193</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1744</v>
+        <v>-0.1408</v>
       </c>
       <c r="V17" t="n">
         <v>-0.9304</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>M. SANTOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2993</v>
+        <v>-0.8728</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2061</v>
+        <v>0.3873</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5054</v>
+        <v>-1.2602</v>
       </c>
       <c r="G18" t="n">
-        <v>1.0186</v>
+        <v>-2.2263</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0888</v>
+        <v>-0.2556</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0702</v>
+        <v>-1.9708</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1795</v>
+        <v>-1.0862</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1427</v>
+        <v>-0.4839</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0368</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1609</v>
+        <v>-1.1401</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0539</v>
+        <v>0.2283</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.107</v>
+        <v>-1.3684</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7569</v>
+        <v>0.4257</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8847</v>
+        <v>0.4013</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1278</v>
+        <v>0.0244</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.5387</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3943</v>
+        <v>-1.2694</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2743</v>
+        <v>0.8024</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6685</v>
+        <v>-2.0718</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4239</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>1.339</v>
+        <v>0.4639</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1562</v>
+        <v>0.6844</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1828</v>
+        <v>-0.2205</v>
       </c>
       <c r="V19" t="n">
         <v>-2.3969</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SANTOS</t>
+          <t>J. DOWTIN JR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,40 +1969,40 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4511</v>
+        <v>-1.5351</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9771</v>
+        <v>-1.8621</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4282</v>
+        <v>0.327</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2263</v>
+        <v>-2.3394</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2556</v>
+        <v>-2.9618</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9708</v>
+        <v>0.6224</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0862</v>
+        <v>-2.4287</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4839</v>
+        <v>-3.0544</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.6257</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1401</v>
+        <v>0.0893</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2283</v>
+        <v>0.0926</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3684</v>
+        <v>-0.0033</v>
       </c>
       <c r="P20" t="n">
         <v>0.9278</v>
@@ -2014,28 +2014,28 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8474</v>
+        <v>-0.2653</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9911</v>
+        <v>0.4248</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1436</v>
+        <v>-0.6901</v>
       </c>
       <c r="V20" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.1418</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.0722</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. DOWTIN JR</t>
+          <t>O. BRISSETT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4445</v>
+        <v>-2.3747</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5698</v>
+        <v>-1.6965</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1253</v>
+        <v>-0.6782</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.3394</v>
+        <v>-4.0567</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9618</v>
+        <v>-3.1333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6224</v>
+        <v>-0.9234</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4287</v>
+        <v>-3.2702</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.0544</v>
+        <v>-2.6679</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6257</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0893</v>
+        <v>-0.7865</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0926</v>
+        <v>-0.4655</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0033</v>
+        <v>-0.3211</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1747</v>
+        <v>1.6641</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>0.9834000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8918</v>
+        <v>0.6807</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1418</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.428</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2926</v>
+        <v>-2.6528</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0487</v>
+        <v>-2.5769</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2439</v>
+        <v>-0.0759</v>
       </c>
       <c r="G22" t="n">
         <v>1.6903</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.344</v>
+        <v>0.2959</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1731</v>
+        <v>0.6449</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5171</v>
+        <v>-0.349</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6189</v>
+        <v>-5.4894</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0861</v>
+        <v>-5.7886</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4672</v>
+        <v>0.2992</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2152</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3677</v>
+        <v>0.7617</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5658</v>
+        <v>0.7316</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1981</v>
+        <v>0.0301</v>
       </c>
       <c r="V23" t="n">
         <v>0.8197</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.5617</v>
+        <v>-10.5615</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2620000000000022</v>
+        <v>-0.2621000000000011</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.2997</v>
+        <v>-10.2996</v>
       </c>
       <c r="G24" t="n">
         <v>-6.290700000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.931700000000001</v>
+        <v>-3.9317</v>
       </c>
       <c r="I24" t="n">
         <v>-2.3592</v>
@@ -2302,10 +2302,10 @@
         <v>1.967199999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2271</v>
+        <v>-1.227099999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>3.194400000000001</v>
+        <v>3.1944</v>
       </c>
       <c r="M24" t="n">
         <v>-8.257899999999999</v>
@@ -2326,19 +2326,19 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>4.7575</v>
+        <v>4.7577</v>
       </c>
       <c r="T24" t="n">
-        <v>6.352300000000001</v>
+        <v>6.3522</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5946</v>
+        <v>-1.5945</v>
       </c>
       <c r="V24" t="n">
         <v>-7.8686</v>
       </c>
       <c r="W24" t="n">
-        <v>6.4954</v>
+        <v>6.495399999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-14.364</v>
